--- a/artfynd/A 39925-2025 artfynd.xlsx
+++ b/artfynd/A 39925-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>124732310</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39925-2025 artfynd.xlsx
+++ b/artfynd/A 39925-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>124732310</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39925-2025 artfynd.xlsx
+++ b/artfynd/A 39925-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>124732310</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39925-2025 artfynd.xlsx
+++ b/artfynd/A 39925-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>124732310</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
